--- a/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_MFH_from_2015_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_MFH_from_2015_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>34.82796165333333</v>
+        <v>22.45133877997805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>5490.939486141</v>
       </c>
       <c r="F2" t="n">
-        <v>34.82796165333333</v>
+        <v>23.20018287584099</v>
       </c>
       <c r="G2" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="H2" t="n">
-        <v>39.70037654623641</v>
+        <v>22.62990064357673</v>
       </c>
       <c r="I2" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="J2" t="n">
-        <v>39.70037654623641</v>
+        <v>22.73091204063722</v>
       </c>
       <c r="K2" t="n">
         <v>5490.939486141</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>34.82796165333333</v>
+        <v>22.45133877997805</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>5490.939486141</v>
       </c>
       <c r="F3" t="n">
-        <v>34.82796165333333</v>
+        <v>23.20018287584098</v>
       </c>
       <c r="G3" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="H3" t="n">
-        <v>39.70037654623641</v>
+        <v>22.62990064357673</v>
       </c>
       <c r="I3" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="J3" t="n">
-        <v>39.70037654623641</v>
+        <v>22.73091204063722</v>
       </c>
       <c r="K3" t="n">
         <v>5490.939486141</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>34.82796165333333</v>
+        <v>22.45133877997805</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>5490.939486141</v>
       </c>
       <c r="F4" t="n">
-        <v>34.82796165333333</v>
+        <v>23.20018287584099</v>
       </c>
       <c r="G4" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="H4" t="n">
-        <v>39.70037654623641</v>
+        <v>22.62990064357673</v>
       </c>
       <c r="I4" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="J4" t="n">
-        <v>39.70037654623641</v>
+        <v>22.73091204063722</v>
       </c>
       <c r="K4" t="n">
         <v>5490.939486141</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82796165333333</v>
+        <v>22.45133877997805</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>5490.939486141</v>
       </c>
       <c r="F5" t="n">
-        <v>34.82796165333333</v>
+        <v>23.20018287584099</v>
       </c>
       <c r="G5" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="H5" t="n">
-        <v>41.22864048434102</v>
+        <v>22.62990064357674</v>
       </c>
       <c r="I5" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="J5" t="n">
-        <v>41.36252922781919</v>
+        <v>22.73091204063722</v>
       </c>
       <c r="K5" t="n">
         <v>5490.939486141</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>34.82796165333333</v>
+        <v>22.98744542653136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>5490.939486141</v>
       </c>
       <c r="F6" t="n">
-        <v>34.82796165333333</v>
+        <v>23.33809119294988</v>
       </c>
       <c r="G6" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="H6" t="n">
-        <v>41.22864048434102</v>
+        <v>23.87395855798685</v>
       </c>
       <c r="I6" t="n">
         <v>5490.939486141</v>
       </c>
       <c r="J6" t="n">
-        <v>41.36252922781919</v>
+        <v>22.73091204063722</v>
       </c>
       <c r="K6" t="n">
         <v>5490.939486141</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>8.2364092292115</v>
+        <v>17.68642179775281</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00372001448</v>
+        <v>0.0032347952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.003879600827982656</v>
+        <v>0.003372579864956694</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00372001448</v>
+        <v>0.0032347952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003879600827982656</v>
+        <v>0.003372579864956694</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003881754239999871</v>
+        <v>0.0032347952</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00372001448</v>
+        <v>0.0032347952</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.003879600827982656</v>
+        <v>0.003372579864956694</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00388175424000001</v>
+        <v>0.0032347952</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00388175424</v>
+        <v>0.003372579864956694</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00388175424</v>
+        <v>0.003372579864956694</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00388175424</v>
+        <v>0.0032347952</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2719848973994263</v>
+        <v>0.2266168799055875</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2719848973994263</v>
+        <v>0.2292333388824999</v>
       </c>
       <c r="G17" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2719848973994283</v>
+        <v>0.2116485938995875</v>
       </c>
       <c r="I17" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2719848973994283</v>
+        <v>0.2122426083556702</v>
       </c>
       <c r="K17" t="n">
         <v>0.5774109432</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2719848973994263</v>
+        <v>0.2266168799055875</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2719848973994263</v>
+        <v>0.2292333388824999</v>
       </c>
       <c r="G18" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2719848973994283</v>
+        <v>0.2116485938995875</v>
       </c>
       <c r="I18" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2719848973994283</v>
+        <v>0.2122426083556702</v>
       </c>
       <c r="K18" t="n">
         <v>0.5774109432</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2719848973994263</v>
+        <v>0.2266168799055875</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2719848973994263</v>
+        <v>0.2292333388824999</v>
       </c>
       <c r="G19" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2719848973994283</v>
+        <v>0.2116485938995875</v>
       </c>
       <c r="I19" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2719848973994283</v>
+        <v>0.2122426083556702</v>
       </c>
       <c r="K19" t="n">
         <v>0.5774109432</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2599740919264694</v>
+        <v>0.1975897213196195</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2599740919264694</v>
+        <v>0.1958683850378318</v>
       </c>
       <c r="G20" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2599740919264693</v>
+        <v>0.08975560980409883</v>
       </c>
       <c r="I20" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2599740919264693</v>
+        <v>0.09014411575787951</v>
       </c>
       <c r="K20" t="n">
         <v>0.5774109432</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2599740919264694</v>
+        <v>0.1975897213196195</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2599740919264694</v>
+        <v>0.1958683850378318</v>
       </c>
       <c r="G21" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2599740919264693</v>
+        <v>0.08975560980409883</v>
       </c>
       <c r="I21" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2599740919264693</v>
+        <v>0.09014411575787951</v>
       </c>
       <c r="K21" t="n">
         <v>0.5774109432</v>
@@ -1419,7 +1419,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.0567162363252638</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1433,19 +1433,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.05409977734835134</v>
       </c>
       <c r="G27" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.07168452233126381</v>
       </c>
       <c r="I27" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.07109050787518108</v>
       </c>
       <c r="K27" t="n">
         <v>0.5774109432</v>
@@ -1456,7 +1456,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.07346563334636116</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1470,19 +1470,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.07105288523678943</v>
       </c>
       <c r="G28" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.1202939465</v>
       </c>
       <c r="I28" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.1158213515082738</v>
       </c>
       <c r="K28" t="n">
         <v>0.5774109432</v>
@@ -1493,7 +1493,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.1167308948722689</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,19 +1507,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.1094499300360195</v>
       </c>
       <c r="G29" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.1644569069230226</v>
       </c>
       <c r="I29" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1596824565199888</v>
       </c>
       <c r="K29" t="n">
         <v>0.5774109432</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.06477232185424631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.06649365813603399</v>
       </c>
       <c r="G30" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.1726064333697669</v>
       </c>
       <c r="I30" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.1722179274159862</v>
       </c>
       <c r="K30" t="n">
         <v>0.5774109432</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.04802292483314894</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>0.5774109432</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.04954055024759588</v>
       </c>
       <c r="G31" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.1505802508227748</v>
       </c>
       <c r="I31" t="n">
         <v>0.5774109432</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.1545248035147979</v>
       </c>
       <c r="K31" t="n">
         <v>0.5774109432</v>
@@ -2142,13 +2142,13 @@
         <v>2.237928745729624</v>
       </c>
       <c r="H46" t="n">
-        <v>2.237928745729624</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>2.237928745729624</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2.237928745729624</v>
       </c>
       <c r="K46" t="n">
         <v>2.237928745729624</v>
@@ -2159,7 +2159,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1831747224404092</v>
+        <v>0.1487488777256279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2173,19 +2173,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2189804712685943</v>
+        <v>0.1627970699967946</v>
       </c>
       <c r="G47" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2204936612482657</v>
+        <v>0.1460461660730938</v>
       </c>
       <c r="I47" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1908214811955735</v>
+        <v>0.1632202434596448</v>
       </c>
       <c r="K47" t="n">
         <v>1.507877256849721</v>
@@ -2196,7 +2196,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1831747224404092</v>
+        <v>0.1487488777256279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2210,19 +2210,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2189804712685943</v>
+        <v>0.1627970699967946</v>
       </c>
       <c r="G48" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2204936612482657</v>
+        <v>0.1460461660730938</v>
       </c>
       <c r="I48" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1908214811955735</v>
+        <v>0.1632202434596448</v>
       </c>
       <c r="K48" t="n">
         <v>1.507877256849721</v>
@@ -2233,7 +2233,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1831747224404092</v>
+        <v>0.1487488777256279</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2247,19 +2247,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2189804712685943</v>
+        <v>0.1627970699967946</v>
       </c>
       <c r="G49" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2204936612482657</v>
+        <v>0.1460461660730938</v>
       </c>
       <c r="I49" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J49" t="n">
-        <v>0.1908214811955735</v>
+        <v>0.1632202434596448</v>
       </c>
       <c r="K49" t="n">
         <v>1.507877256849721</v>
@@ -2344,7 +2344,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.4209809733780622</v>
+        <v>0.422996994700569</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2358,19 +2358,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2728164027437887</v>
+        <v>0.2816757545415566</v>
       </c>
       <c r="G52" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2629090202979717</v>
+        <v>0.4221014537329412</v>
       </c>
       <c r="I52" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J52" t="n">
-        <v>0.4127210159403971</v>
+        <v>0.2758500785781517</v>
       </c>
       <c r="K52" t="n">
         <v>1.507877256849721</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.4209809733780622</v>
+        <v>0.422996994700569</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2728164027437887</v>
+        <v>0.2816757545415566</v>
       </c>
       <c r="G53" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2629090202979717</v>
+        <v>0.4221014537329412</v>
       </c>
       <c r="I53" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4127210159403971</v>
+        <v>0.2758500785781517</v>
       </c>
       <c r="K53" t="n">
         <v>1.507877256849721</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.4209809733780621</v>
+        <v>0.422996994700569</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2728164027437887</v>
+        <v>0.2816757545415566</v>
       </c>
       <c r="G54" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2629090202979717</v>
+        <v>0.4221014537329412</v>
       </c>
       <c r="I54" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J54" t="n">
-        <v>0.4127210159403971</v>
+        <v>0.2758500785781517</v>
       </c>
       <c r="K54" t="n">
         <v>1.507877256849721</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.4617611539268163</v>
+        <v>0.4585674287951311</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4507507628048905</v>
+        <v>0.4471232133400597</v>
       </c>
       <c r="G55" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4384554602063628</v>
+        <v>0.4480422686105229</v>
       </c>
       <c r="I55" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4565474466548521</v>
+        <v>0.4480903403530506</v>
       </c>
       <c r="K55" t="n">
         <v>1.507877256849721</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.5150261598987744</v>
+        <v>0.496211283777966</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F56" t="n">
-        <v>0.473634491311363</v>
+        <v>0.4741616550925592</v>
       </c>
       <c r="G56" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4530500122597615</v>
+        <v>0.5013676799917228</v>
       </c>
       <c r="I56" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5056594593890159</v>
+        <v>0.4820924143418971</v>
       </c>
       <c r="K56" t="n">
         <v>1.507877256849721</v>
@@ -2714,7 +2714,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2044100556111839</v>
+        <v>0.07864493458225613</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2728,19 +2728,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1986768993113635</v>
+        <v>0.089742916758067</v>
       </c>
       <c r="G62" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1723090389990922</v>
+        <v>0.07920829237461155</v>
       </c>
       <c r="I62" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1737168504929718</v>
+        <v>0.09722032520330029</v>
       </c>
       <c r="K62" t="n">
         <v>1.507877256849721</v>
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2044100556111839</v>
+        <v>0.07864493458225613</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,19 +2765,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1986768993113635</v>
+        <v>0.089742916758067</v>
       </c>
       <c r="G63" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1723090389990922</v>
+        <v>0.07920829237461155</v>
       </c>
       <c r="I63" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1737168504929718</v>
+        <v>0.09722032520330029</v>
       </c>
       <c r="K63" t="n">
         <v>1.507877256849721</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2044100556111839</v>
+        <v>0.07864493458225613</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1986768993113635</v>
+        <v>0.089742916758067</v>
       </c>
       <c r="G64" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1723090389990922</v>
+        <v>0.07920829237461155</v>
       </c>
       <c r="I64" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1737168504929718</v>
+        <v>0.09722032520330029</v>
       </c>
       <c r="K64" t="n">
         <v>1.507877256849721</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2159015657466012</v>
+        <v>0.1130048155000575</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2269119568685271</v>
+        <v>0.1262885552902848</v>
       </c>
       <c r="G65" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2092040774467061</v>
+        <v>0.130108968552346</v>
       </c>
       <c r="I65" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1904844875131629</v>
+        <v>0.1298451234468113</v>
       </c>
       <c r="K65" t="n">
         <v>1.507877256849721</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.219558383782647</v>
+        <v>0.1130048155000575</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2609500523700584</v>
+        <v>0.1314356239378301</v>
       </c>
       <c r="G66" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2515313494013113</v>
+        <v>0.130108968552346</v>
       </c>
       <c r="I66" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J66" t="n">
-        <v>0.198294298787003</v>
+        <v>0.1438571850867755</v>
       </c>
       <c r="K66" t="n">
         <v>1.507877256849721</v>
@@ -3269,7 +3269,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.09570921452844616</v>
+        <v>0.1064267426833384</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3283,19 +3283,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2138011926343549</v>
+        <v>0.2157729148308488</v>
       </c>
       <c r="G77" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H77" t="n">
-        <v>0.2257238006022885</v>
+        <v>0.1084027962480877</v>
       </c>
       <c r="I77" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1041761735186757</v>
+        <v>0.2188690809065678</v>
       </c>
       <c r="K77" t="n">
         <v>1.507877256849721</v>
@@ -3306,7 +3306,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.09570921452844616</v>
+        <v>0.1064267426833384</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3320,19 +3320,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2138011926343549</v>
+        <v>0.2157729148308488</v>
       </c>
       <c r="G78" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H78" t="n">
-        <v>0.2257238006022885</v>
+        <v>0.1084027962480877</v>
       </c>
       <c r="I78" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J78" t="n">
-        <v>0.1041761735186757</v>
+        <v>0.2188690809065678</v>
       </c>
       <c r="K78" t="n">
         <v>1.507877256849721</v>
@@ -3343,7 +3343,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.09570921452844616</v>
+        <v>0.1064267426833384</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3357,19 +3357,19 @@
         <v>1.507877256849721</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2138011926343549</v>
+        <v>0.2157729148308488</v>
       </c>
       <c r="G79" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2257238006022885</v>
+        <v>0.1084027962480877</v>
       </c>
       <c r="I79" t="n">
         <v>1.507877256849721</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1041761735186757</v>
+        <v>0.2188690809065678</v>
       </c>
       <c r="K79" t="n">
         <v>1.507877256849721</v>
